--- a/backend/test_media/imports/history.xlsx
+++ b/backend/test_media/imports/history.xlsx
@@ -455,7 +455,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>707</v>
+        <v>711</v>
       </c>
       <c r="D2" t="n">
         <v>14</v>
